--- a/03_Outputs/Penderisco_Sinifana/02_Demografia/demografia.xlsx
+++ b/03_Outputs/Penderisco_Sinifana/02_Demografia/demografia.xlsx
@@ -2495,7 +2495,7 @@
         <v>8.61726103672279</v>
       </c>
       <c r="F4" s="82">
-        <v>4.32616675406398</v>
+        <v>4.32616675406397</v>
       </c>
       <c r="G4" s="84">
         <v>28.4376045500167</v>
